--- a/data/prices.xlsx
+++ b/data/prices.xlsx
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>74100</v>
+        <v>85600</v>
       </c>
     </row>
     <row r="42">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>48200</v>
+        <v>74100</v>
       </c>
     </row>
     <row r="43">
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>95000</v>
+        <v>48200</v>
       </c>
     </row>
     <row r="44">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>68000</v>
+        <v>95000</v>
       </c>
     </row>
     <row r="45">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>34100</v>
+        <v>68000</v>
       </c>
     </row>
     <row r="46">
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>73000</v>
+        <v>34100</v>
       </c>
     </row>
     <row r="47">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>285600</v>
+        <v>73000</v>
       </c>
     </row>
     <row r="48">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>74300</v>
+        <v>285600</v>
       </c>
     </row>
     <row r="49">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>78500</v>
+        <v>74300</v>
       </c>
     </row>
     <row r="50">
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>139800</v>
+        <v>78500</v>
       </c>
     </row>
     <row r="51">
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>24900</v>
+        <v>139800</v>
       </c>
     </row>
     <row r="52">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>28600</v>
+        <v>24900</v>
       </c>
     </row>
     <row r="53">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>136700</v>
+        <v>28600</v>
       </c>
     </row>
     <row r="54">
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>24100</v>
+        <v>136700</v>
       </c>
     </row>
     <row r="55">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>27400</v>
+        <v>24100</v>
       </c>
     </row>
     <row r="56">
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>126000</v>
+        <v>27400</v>
       </c>
     </row>
     <row r="57">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>57800</v>
+        <v>126000</v>
       </c>
     </row>
     <row r="58">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>22800</v>
+        <v>57800</v>
       </c>
     </row>
     <row r="59">
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>67900</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="60">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>26500</v>
+        <v>67900</v>
       </c>
     </row>
     <row r="61">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>327100</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="62">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>163300</v>
+        <v>327100</v>
       </c>
     </row>
     <row r="63">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>106900</v>
+        <v>163300</v>
       </c>
     </row>
     <row r="64">
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>20900</v>
+        <v>106900</v>
       </c>
     </row>
     <row r="65">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>60500</v>
+        <v>20900</v>
       </c>
     </row>
     <row r="66">
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>54300</v>
+        <v>60500</v>
       </c>
     </row>
     <row r="67">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>223400</v>
+        <v>54300</v>
       </c>
     </row>
     <row r="68">
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>39200</v>
+        <v>223400</v>
       </c>
     </row>
     <row r="69">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>180600</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="70">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>156800</v>
+        <v>180600</v>
       </c>
     </row>
     <row r="71">
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>33200</v>
+        <v>156800</v>
       </c>
     </row>
     <row r="72">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>17900</v>
+        <v>33200</v>
       </c>
     </row>
     <row r="73">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>290400</v>
+        <v>17900</v>
       </c>
     </row>
     <row r="74">
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>60900</v>
+        <v>290400</v>
       </c>
     </row>
     <row r="75">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>78700</v>
+        <v>60900</v>
       </c>
     </row>
     <row r="76">
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>27400</v>
+        <v>78700</v>
       </c>
     </row>
     <row r="77">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>258500</v>
+        <v>27400</v>
       </c>
     </row>
     <row r="78">
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>125600</v>
+        <v>258500</v>
       </c>
     </row>
     <row r="79">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>57200</v>
+        <v>125600</v>
       </c>
     </row>
     <row r="80">
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>54800</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="81">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>34800</v>
+        <v>54800</v>
       </c>
     </row>
     <row r="82">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>185400</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="83">
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>237600</v>
+        <v>185400</v>
       </c>
     </row>
     <row r="84">
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>34100</v>
+        <v>237600</v>
       </c>
     </row>
     <row r="85">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>30100</v>
+        <v>34100</v>
       </c>
     </row>
     <row r="86">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>118900</v>
+        <v>30100</v>
       </c>
     </row>
     <row r="87">
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>41200</v>
+        <v>118900</v>
       </c>
     </row>
     <row r="88">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>69000</v>
+        <v>41200</v>
       </c>
     </row>
     <row r="89">
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>317600</v>
+        <v>69000</v>
       </c>
     </row>
     <row r="90">
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>53800</v>
+        <v>317600</v>
       </c>
     </row>
     <row r="91">
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>299800</v>
+        <v>53800</v>
       </c>
     </row>
     <row r="92">
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>304400</v>
+        <v>299800</v>
       </c>
     </row>
     <row r="93">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>30400</v>
+        <v>304400</v>
       </c>
     </row>
     <row r="94">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>17700</v>
+        <v>30400</v>
       </c>
     </row>
     <row r="95">
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>127000</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="96">
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>45600</v>
+        <v>127000</v>
       </c>
     </row>
     <row r="97">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11700</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="98">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>8100</v>
+        <v>11700</v>
       </c>
     </row>
     <row r="99">
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>138000</v>
+        <v>8100</v>
       </c>
     </row>
     <row r="100">
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>40000</v>
+        <v>138000</v>
       </c>
     </row>
     <row r="101">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>42000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="102">
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>43100</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="103">
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>153300</v>
+        <v>43100</v>
       </c>
     </row>
     <row r="104">
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>24500</v>
+        <v>153300</v>
       </c>
     </row>
     <row r="105">
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>493400</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="106">
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>45400</v>
+        <v>493400</v>
       </c>
     </row>
     <row r="107">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>67500</v>
+        <v>45400</v>
       </c>
     </row>
     <row r="108">
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>33700</v>
+        <v>67500</v>
       </c>
     </row>
     <row r="109">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>9700</v>
+        <v>33700</v>
       </c>
     </row>
     <row r="110">
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>40400</v>
+        <v>9700</v>
       </c>
     </row>
     <row r="111">
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>33200</v>
+        <v>40400</v>
       </c>
     </row>
     <row r="112">
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>28000</v>
+        <v>33200</v>
       </c>
     </row>
     <row r="113">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>85500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="114">
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>18500</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="115">
@@ -1929,7 +1929,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>74600</v>
+        <v>18500</v>
       </c>
     </row>
     <row r="116">
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>98300</v>
+        <v>74600</v>
       </c>
     </row>
     <row r="117">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>52000</v>
+        <v>98300</v>
       </c>
     </row>
     <row r="118">
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>18400</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="119">
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>173200</v>
+        <v>18400</v>
       </c>
     </row>
     <row r="120">
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>172300</v>
+        <v>173200</v>
       </c>
     </row>
     <row r="121">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11100</v>
+        <v>172300</v>
       </c>
     </row>
     <row r="122">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>79300</v>
+        <v>11100</v>
       </c>
     </row>
     <row r="123">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>86200</v>
+        <v>79300</v>
       </c>
     </row>
     <row r="124">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>19900</v>
+        <v>86200</v>
       </c>
     </row>
     <row r="125">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>21400</v>
+        <v>19900</v>
       </c>
     </row>
     <row r="126">
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>96100</v>
+        <v>21400</v>
       </c>
     </row>
     <row r="127">
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>30500</v>
+        <v>96100</v>
       </c>
     </row>
     <row r="128">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>178600</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="129">
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>114600</v>
+        <v>178600</v>
       </c>
     </row>
     <row r="130">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>64500</v>
+        <v>114600</v>
       </c>
     </row>
     <row r="131">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>71000</v>
+        <v>64500</v>
       </c>
     </row>
     <row r="132">
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>87100</v>
+        <v>71000</v>
       </c>
     </row>
     <row r="133">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>91900</v>
+        <v>87100</v>
       </c>
     </row>
     <row r="134">
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>98800</v>
+        <v>91900</v>
       </c>
     </row>
     <row r="135">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>207700</v>
+        <v>98800</v>
       </c>
     </row>
     <row r="136">
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>75500</v>
+        <v>207700</v>
       </c>
     </row>
     <row r="137">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>100400</v>
+        <v>75500</v>
       </c>
     </row>
     <row r="138">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>19800</v>
+        <v>100400</v>
       </c>
     </row>
     <row r="139">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>242800</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="140">
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>213600</v>
+        <v>242800</v>
       </c>
     </row>
     <row r="141">
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>111500</v>
+        <v>213600</v>
       </c>
     </row>
     <row r="142">
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>37000</v>
+        <v>111500</v>
       </c>
     </row>
     <row r="143">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>190500</v>
+        <v>37000</v>
       </c>
     </row>
     <row r="144">
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>137700</v>
+        <v>190500</v>
       </c>
     </row>
     <row r="145">
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>24300</v>
+        <v>137700</v>
       </c>
     </row>
     <row r="146">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>157900</v>
+        <v>24300</v>
       </c>
     </row>
     <row r="147">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>38800</v>
+        <v>157900</v>
       </c>
     </row>
     <row r="148">
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>18600</v>
+        <v>38800</v>
       </c>
     </row>
     <row r="149">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>31300</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="150">
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>41700</v>
+        <v>31300</v>
       </c>
     </row>
     <row r="151">
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>35500</v>
+        <v>41700</v>
       </c>
     </row>
     <row r="152">
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>66200</v>
+        <v>35500</v>
       </c>
     </row>
     <row r="153">
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>84300</v>
+        <v>66200</v>
       </c>
     </row>
     <row r="154">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>29500</v>
+        <v>84300</v>
       </c>
     </row>
     <row r="155">
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>154300</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="156">
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>116300</v>
+        <v>154300</v>
       </c>
     </row>
     <row r="157">
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>146100</v>
+        <v>116300</v>
       </c>
     </row>
     <row r="158">
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>315400</v>
+        <v>146100</v>
       </c>
     </row>
     <row r="159">
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>54300</v>
+        <v>315400</v>
       </c>
     </row>
     <row r="160">
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>123500</v>
+        <v>54300</v>
       </c>
     </row>
     <row r="161">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>68600</v>
+        <v>123500</v>
       </c>
     </row>
     <row r="162">
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>137700</v>
+        <v>68600</v>
       </c>
     </row>
     <row r="163">
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>130900</v>
+        <v>137700</v>
       </c>
     </row>
     <row r="164">
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>75700</v>
+        <v>130900</v>
       </c>
     </row>
     <row r="165">
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>118900</v>
+        <v>75700</v>
       </c>
     </row>
     <row r="166">
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>268300</v>
+        <v>118900</v>
       </c>
     </row>
     <row r="167">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>82200</v>
+        <v>268300</v>
       </c>
     </row>
     <row r="168">
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>137000</v>
+        <v>82200</v>
       </c>
     </row>
     <row r="169">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>49100</v>
+        <v>137000</v>
       </c>
     </row>
     <row r="170">
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>61400</v>
+        <v>49100</v>
       </c>
     </row>
     <row r="171">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>133100</v>
+        <v>61400</v>
       </c>
     </row>
     <row r="172">
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>30000</v>
+        <v>133100</v>
       </c>
     </row>
     <row r="173">
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>63300</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="174">
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>178600</v>
+        <v>63300</v>
       </c>
     </row>
     <row r="175">
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>139600</v>
+        <v>178600</v>
       </c>
     </row>
     <row r="176">
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>30300</v>
+        <v>139600</v>
       </c>
     </row>
     <row r="177">
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>18300</v>
+        <v>30300</v>
       </c>
     </row>
     <row r="178">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>50500</v>
+        <v>18300</v>
       </c>
     </row>
     <row r="180">
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>9300</v>
+        <v>50500</v>
       </c>
     </row>
     <row r="181">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>132200</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="182">
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>21000</v>
+        <v>132200</v>
       </c>
     </row>
     <row r="183">
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>82200</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="184">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>14800</v>
+        <v>82200</v>
       </c>
     </row>
     <row r="185">
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>70200</v>
+        <v>14800</v>
       </c>
     </row>
     <row r="186">
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>233200</v>
+        <v>70200</v>
       </c>
     </row>
     <row r="187">
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>74700</v>
+        <v>233200</v>
       </c>
     </row>
     <row r="188">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>75700</v>
+        <v>74700</v>
       </c>
     </row>
     <row r="189">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>45100</v>
+        <v>75700</v>
       </c>
     </row>
     <row r="190">
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>29900</v>
+        <v>45100</v>
       </c>
     </row>
     <row r="191">
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>104100</v>
+        <v>29900</v>
       </c>
     </row>
     <row r="192">
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>155900</v>
+        <v>104100</v>
       </c>
     </row>
     <row r="193">
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>62400</v>
+        <v>155900</v>
       </c>
     </row>
     <row r="194">
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>20900</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="195">
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>129300</v>
+        <v>20900</v>
       </c>
     </row>
     <row r="196">
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>216600</v>
+        <v>129300</v>
       </c>
     </row>
     <row r="197">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>196400</v>
+        <v>216600</v>
       </c>
     </row>
     <row r="198">
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>36900</v>
+        <v>196400</v>
       </c>
     </row>
     <row r="199">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>178500</v>
+        <v>36900</v>
       </c>
     </row>
     <row r="200">
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>173400</v>
+        <v>178500</v>
       </c>
     </row>
     <row r="201">

--- a/data/prices.xlsx
+++ b/data/prices.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D201"/>
+  <dimension ref="A1:D176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Rectiofar 3ml pharmedic (h/50túi)</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -469,7 +469,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Rectiofar 5ml pharmedic (h/40túi)</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -482,7 +482,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Efferalgan 150mg UPSA SAS (H/12g)</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -495,7 +495,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Combo 20 Nhỏ Mắt Sanlein 0.1% Santen (C/5ml)</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -508,7 +508,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Atasic cefixim 200mg usp (h/30v)</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Nyst thuốc rơ miệng opc (h/10g)</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -534,7 +534,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Combo 3 Diamicron MR 60mg Servier (H/30v)</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Băng thun y tế 3 móc 0.1m x 3m bảo thạch (lốc/10 cuộn)</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -560,7 +560,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Oxy già VP 3% Vĩnh Phúc (lốc/10c/60ml)</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -573,7 +573,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Combo 12 Cao xoa bóp bạch hổ hoạt lạc bảo linh (Lọ/20gr)</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -586,7 +586,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Cefalexin 500mg domesco (h/100v)</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -599,7 +599,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Amoxicillin 500 mekophar (h/100v)</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -612,7 +612,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Kamoxazol 800mg/160mg khapharco (h/100v)</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -625,7 +625,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Combo 10 Nhỏ mắt mũi natri clorid 0.9% pharmedic (lốc/10c/10ml)</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Khẩu trang Trẻ em 4D Bisou KF94 KIDS Dorio (Lốc/10g/10c)</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -651,7 +651,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Combo 10 Postinor 1 gedeon richter (h/1v)</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Bocinor Levonorgestrel 1.5mg ba đình (lốc/10h/1v)</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -677,7 +677,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>A.T Desloratadin syrup 0.5mg/ml An Thiên (H/30g/5ml)</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -690,7 +690,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Khẩu Trang Y Tế 4 Lớp Màu Trắng Thiên Thủy (H/50c)</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Bông y tế Trung Tín (Lốc/20b/25gr)</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -716,7 +716,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Kavasdin amlodipin 5mg khapharco (h/100v)</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -729,7 +729,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Que thử thai chip chips nhất nhất (h/1q)</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -742,7 +742,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Lipistad Atorvastatin 10mg Stella (H/50v)</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -755,7 +755,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Furosemide 40mg mekophar (h/300v)</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -768,7 +768,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Loperamid 2mg khapharco (h/100v)</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -781,7 +781,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Combo 10 Jikagra sildenafil 50mg gia nguyễn (h/4v)</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -794,7 +794,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Nhỏ mắt pataday novartis (c/2.5ml)</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -807,7 +807,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Efferalgan 80mg UPSA SAS (H/12g)</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -820,7 +820,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Vitamin b12 1000mcg fresenius kabi (h/100o/1ml)</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -833,7 +833,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Simethicone 80mg khapharco (h/200v)</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Efferalgan 80mg UPSA SAS (H/10v)</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Nhỏ Mắt Alegysal 0.1% Santen (C/5ml)</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -872,7 +872,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Salonpas dán hisamitsu (H/10h/20m)</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Bọt cạo râu hương chanh Gillette Foamy Lemon Lime Thai Daizo (C/175gr)</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -898,7 +898,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Gynofar 500 pharmedic (c/500ml)</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Soslac g3 ampharco (lốc/10tube/15gr)</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -924,7 +924,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Băng gạc tiệt trùng urgosterile 8cmx10cm urgo (h/50m)</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -937,7 +937,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Dermatix ultra medical (tuýp/7g)(nhỏ)</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Làm mát và dịu mắt vizulize cooling soothing intershop (c/10ml)</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -963,11 +963,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Waisan eperison 50mg bidiphar (h/100v)</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>85600</v>
+        <v>74100</v>
       </c>
     </row>
     <row r="42">
@@ -976,11 +976,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Nifedipin 20 retard hasan (h/100v)</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>74100</v>
+        <v>48200</v>
       </c>
     </row>
     <row r="43">
@@ -989,11 +989,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Làm dịu và giảm khô mắt vizulize intensive dry eyes intershop (c/10ml)</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>48200</v>
+        <v>95000</v>
       </c>
     </row>
     <row r="44">
@@ -1002,11 +1002,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Lostad T50 Losartan 50mg Stella (H/30v)</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>95000</v>
+        <v>68000</v>
       </c>
     </row>
     <row r="45">
@@ -1015,11 +1015,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Cồn 90 độ Vĩnh Phúc (lốc/10c) (xanh)</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>68000</v>
+        <v>34100</v>
       </c>
     </row>
     <row r="46">
@@ -1028,11 +1028,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Enalapril 5mg Stella (H/100v)</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>34100</v>
+        <v>73000</v>
       </c>
     </row>
     <row r="47">
@@ -1041,11 +1041,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Combo 2 Bột sủi thanh nhiệt sensa cools pt sari (lốc/6h/6g)</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>73000</v>
+        <v>285600</v>
       </c>
     </row>
     <row r="48">
@@ -1054,11 +1054,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Marvelon Organon (H/21v)</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>285600</v>
+        <v>74300</v>
       </c>
     </row>
     <row r="49">
@@ -1067,11 +1067,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Giảm khô mắt Vizulize Dry Eyes Eye Drops Long Lasting Relief East Midlands (C/10ml)</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>74300</v>
+        <v>78500</v>
       </c>
     </row>
     <row r="50">
@@ -1080,11 +1080,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Cefotaxone cefotaxim1g bidiphar (h/10lọ)</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>78500</v>
+        <v>139800</v>
       </c>
     </row>
     <row r="51">
@@ -1093,11 +1093,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Atussin siro ho united pharma (c/60ml)</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>139800</v>
+        <v>24900</v>
       </c>
     </row>
     <row r="52">
@@ -1106,11 +1106,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Băng keo lụa urgosyval strong adhesive tape 2.5cmx5m (cuộn)</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>24900</v>
+        <v>28600</v>
       </c>
     </row>
     <row r="53">
@@ -1119,11 +1119,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Nước muối sinh lý Vĩnh Phúc (thùng/12c/1000ml)</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>28600</v>
+        <v>136700</v>
       </c>
     </row>
     <row r="54">
@@ -1132,11 +1132,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Kéo cắt thuốc size 14 (cái)</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>136700</v>
+        <v>24100</v>
       </c>
     </row>
     <row r="55">
@@ -1145,11 +1145,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Vitamin pp 500mg khapharco (h/100v)</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>24100</v>
+        <v>27400</v>
       </c>
     </row>
     <row r="56">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Nhỏ Mắt Sanlein 0.3% Santen (Chai/5ml)</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>27400</v>
+        <v>126000</v>
       </c>
     </row>
     <row r="57">
@@ -1171,11 +1171,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Nước mắt nhân tạo vizulize hypromellose 0.3% intershop (c/10ml)</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>126000</v>
+        <v>57800</v>
       </c>
     </row>
     <row r="58">
@@ -1184,11 +1184,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Khẩu Trang Y Tế 4 lớp màu xanh Tâm Anh (H/50C)</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>57800</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="59">
@@ -1197,11 +1197,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Băng cá nhân trong suốt urgo transparent (h/100m)</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>22800</v>
+        <v>67900</v>
       </c>
     </row>
     <row r="60">
@@ -1210,11 +1210,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Kem yoosun rau má đại bắc (tube/25g) (xanh)</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>67900</v>
+        <v>26500</v>
       </c>
     </row>
     <row r="61">
@@ -1223,11 +1223,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Mua 10 Nhỏ mắt mũi natri clorid 0,9% pharmedic (lốc/10c/10ml) tặng 1 Povidine 10% pharmedic (c/20ml) (hàng khuyến mãi)</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>26500</v>
+        <v>327100</v>
       </c>
     </row>
     <row r="62">
@@ -1236,11 +1236,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Enterogermina gut defense 2 billion/5ml Opella (H/20o/5ml)</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>327100</v>
+        <v>163300</v>
       </c>
     </row>
     <row r="63">
@@ -1249,11 +1249,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Hỗ trợ tiêu hóa carbo nam việt (lốc/10c/100v)</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>163300</v>
+        <v>106900</v>
       </c>
     </row>
     <row r="64">
@@ -1262,11 +1262,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Gentrisone cream shinpoong (t/20g) (lớn)</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>106900</v>
+        <v>20900</v>
       </c>
     </row>
     <row r="65">
@@ -1275,11 +1275,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Cotrimxazon 960mg pharimexco (h/100v)</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>20900</v>
+        <v>60500</v>
       </c>
     </row>
     <row r="66">
@@ -1288,11 +1288,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>V.rohto new rohto (C/13ml)</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>60500</v>
+        <v>54300</v>
       </c>
     </row>
     <row r="67">
@@ -1301,11 +1301,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Motilium m 10mg janssen (h/100v)</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>54300</v>
+        <v>223400</v>
       </c>
     </row>
     <row r="68">
@@ -1314,11 +1314,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Salonpas Gel Hisamitsu (tuýp/30gr)</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>223400</v>
+        <v>39200</v>
       </c>
     </row>
     <row r="69">
@@ -1327,11 +1327,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Tăm Chỉ Nha Khoa Oraltana Tanaphar (Lốc/6hũ/100c)</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>39200</v>
+        <v>180600</v>
       </c>
     </row>
     <row r="70">
@@ -1340,11 +1340,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Stadnex 40 esomeprazol 40mg stella (h/28v)</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>180600</v>
+        <v>156800</v>
       </c>
     </row>
     <row r="71">
@@ -1353,11 +1353,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Oracortia cream (tuýp/5gr)</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>156800</v>
+        <v>33200</v>
       </c>
     </row>
     <row r="72">
@@ -1366,11 +1366,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Metronidazol 500mg Kabi (C/100ml) (Chai nhựa)</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>33200</v>
+        <v>17900</v>
       </c>
     </row>
     <row r="73">
@@ -1379,11 +1379,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Kim luồn 24g mediflon (H/100c)</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>17900</v>
+        <v>290400</v>
       </c>
     </row>
     <row r="74">
@@ -1392,11 +1392,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Hồ nước HD Pharma (Lốc/10c/20gr)</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>290400</v>
+        <v>60900</v>
       </c>
     </row>
     <row r="75">
@@ -1405,11 +1405,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Cồn boric 3% dp 3/2 (Lốc/10c/10ml)</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>60900</v>
+        <v>78700</v>
       </c>
     </row>
     <row r="76">
@@ -1418,11 +1418,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Ống hít inhaler pharmedic (dây/5c)</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>78700</v>
+        <v>27400</v>
       </c>
     </row>
     <row r="77">
@@ -1431,11 +1431,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Nautamine sanofiaventis (h/80v)</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>27400</v>
+        <v>258500</v>
       </c>
     </row>
     <row r="78">
@@ -1444,11 +1444,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Que thử thai Chip Chips Nhất Nhất Shenzhen (Hộp/12que)</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>258500</v>
+        <v>125600</v>
       </c>
     </row>
     <row r="79">
@@ -1457,11 +1457,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Tetracyclin 500mg Thanh Hóa (H/100v)</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>125600</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="80">
@@ -1470,11 +1470,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Sancoba Santen (C/5ml)</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>57200</v>
+        <v>54800</v>
       </c>
     </row>
     <row r="81">
@@ -1483,11 +1483,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Kary Uni Santen (C/5ml)</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>54800</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="82">
@@ -1496,11 +1496,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Bông cắt miếng y tế 7cm x 7cm bông bạch tuyết (g/1kg)</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>34800</v>
+        <v>185400</v>
       </c>
     </row>
     <row r="83">
@@ -1509,11 +1509,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Lostad T50 Losartan 50mg Stella (H/100v)</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>185400</v>
+        <v>237600</v>
       </c>
     </row>
     <row r="84">
@@ -1522,11 +1522,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Menison 4mg Pymepharco (H/50v)</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>237600</v>
+        <v>34100</v>
       </c>
     </row>
     <row r="85">
@@ -1535,11 +1535,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Cefixim 200mg pharimexco (H/20v)</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>34100</v>
+        <v>30100</v>
       </c>
     </row>
     <row r="86">
@@ -1548,11 +1548,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Phosphalugel sanofi (hộp/26gói/20gram)</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>30100</v>
+        <v>118900</v>
       </c>
     </row>
     <row r="87">
@@ -1561,11 +1561,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Tra Mắt mediclovir Aciclovir 3% medipharco (t/5gr)</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>118900</v>
+        <v>41200</v>
       </c>
     </row>
     <row r="88">
@@ -1574,11 +1574,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Băng cuộn y tế 3 con nai 1m8 x 8.5cm đông fa (h/50c)</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>41200</v>
+        <v>69000</v>
       </c>
     </row>
     <row r="89">
@@ -1587,11 +1587,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Gạc y tế 8x9cm 8 lớp Dopha (Thùng 50gói)</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>69000</v>
+        <v>317600</v>
       </c>
     </row>
     <row r="90">
@@ -1600,11 +1600,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Dầu mù u plus thiên khánh (lốc/10c/12ml)</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>317600</v>
+        <v>53800</v>
       </c>
     </row>
     <row r="91">
@@ -1613,11 +1613,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Janumet 50mg/1000mg msd (h/28v)</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>53800</v>
+        <v>299800</v>
       </c>
     </row>
     <row r="92">
@@ -1626,11 +1626,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Janumet 50mg/850mg msd (h/28v)</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>299800</v>
+        <v>304400</v>
       </c>
     </row>
     <row r="93">
@@ -1639,11 +1639,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Cồn 90 độ Vĩnh Phúc (c/500ml) (xanh)</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>304400</v>
+        <v>30400</v>
       </c>
     </row>
     <row r="94">
@@ -1652,11 +1652,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Katrypsin 4200 iu khapharco (h/100v) (vỉ thường)</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>30400</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="95">
@@ -1665,11 +1665,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Tyrotab pharmedic (lốc/10h/24v)</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>17700</v>
+        <v>127000</v>
       </c>
     </row>
     <row r="96">
@@ -1678,11 +1678,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Jikagra sildenafil 50mg gia nguyễn (h/4v)</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>127000</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="97">
@@ -1691,11 +1691,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Kacerin cetirizine 10mg khapharco (h/100v) (vỉ xanh)</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>45600</v>
+        <v>11700</v>
       </c>
     </row>
     <row r="98">
@@ -1704,11 +1704,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Mifestad 10mg stella (h/1v)</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11700</v>
+        <v>8100</v>
       </c>
     </row>
     <row r="99">
@@ -1717,11 +1717,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Bột sủi thanh nhiệt sensa cools pt sari (lốc/6h/6g)</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>8100</v>
+        <v>138000</v>
       </c>
     </row>
     <row r="100">
@@ -1730,11 +1730,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Calcium hasan 500mg (t/20v)</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>138000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="101">
@@ -1743,11 +1743,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Lostad t25 losartan 25mg stella (h/30v)</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>40000</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="102">
@@ -1756,11 +1756,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Lipistad 20 Atorvastatin 20mg Stella (H/30v)</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>42000</v>
+        <v>43100</v>
       </c>
     </row>
     <row r="103">
@@ -1769,11 +1769,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Polygynax innothera (h/12v)</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>43100</v>
+        <v>153300</v>
       </c>
     </row>
     <row r="104">
@@ -1782,11 +1782,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Khẩu trang Y Tế 4 Lớp Màu Xanh Thiên Thủy (H/50c)</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>153300</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="105">
@@ -1795,11 +1795,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Combo 10 Augbactam 1g mekophar (h/14v)</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>24500</v>
+        <v>493400</v>
       </c>
     </row>
     <row r="106">
@@ -1808,11 +1808,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Efferalgan 500mg UPSA SAS (H/16v)</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>493400</v>
+        <v>45400</v>
       </c>
     </row>
     <row r="107">
@@ -1821,11 +1821,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Băng cá nhân vải độ dính cao Urgo Durable (h/102m)</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>45400</v>
+        <v>67500</v>
       </c>
     </row>
     <row r="108">
@@ -1834,11 +1834,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Postinor 1 gedeon richter (h/1v)</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>67500</v>
+        <v>33700</v>
       </c>
     </row>
     <row r="109">
@@ -1847,11 +1847,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Mắt kính bảo hộ (cái)</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>33700</v>
+        <v>9700</v>
       </c>
     </row>
     <row r="110">
@@ -1860,11 +1860,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Cataflam 25mg novartis (h/10v)</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>9700</v>
+        <v>40400</v>
       </c>
     </row>
     <row r="111">
@@ -1873,11 +1873,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Cồn 90 độ Vĩnh Phúc (chai/500ml) (vòi xịt)</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>40400</v>
+        <v>33200</v>
       </c>
     </row>
     <row r="112">
@@ -1886,11 +1886,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Bao Cao Su Safefit Freezermax (H/10c)</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>33200</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="113">
@@ -1899,11 +1899,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Găng Tay Y Tế Latex Có Bột Trơn Size S Vglove Khải Hoàn (H/100C)</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>28000</v>
+        <v>85500</v>
       </c>
     </row>
     <row r="114">
@@ -1912,11 +1912,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Băng keo lụa urgosyval strong adhesive tape 1.25cmx5m urgo (cuộn)</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>85500</v>
+        <v>18500</v>
       </c>
     </row>
     <row r="115">
@@ -1925,11 +1925,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Stadnolol 50 atenolol 50mg stella (h/100v)</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>18500</v>
+        <v>74600</v>
       </c>
     </row>
     <row r="116">
@@ -1938,11 +1938,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Irbesartan 150mg stella (h/28v)</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>74600</v>
+        <v>98300</v>
       </c>
     </row>
     <row r="117">
@@ -1951,11 +1951,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Gikanin khapharco (h/100v)</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>98300</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="118">
@@ -1964,11 +1964,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Remint-s khapharco (h/100v)</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>52000</v>
+        <v>18400</v>
       </c>
     </row>
     <row r="119">
@@ -1977,11 +1977,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Strepsils orange with vitamin c (h/50g/2v)</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>18400</v>
+        <v>173200</v>
       </c>
     </row>
     <row r="120">
@@ -1990,11 +1990,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Strepsils cool reckitt benckiser (h/50g/2v)</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>173200</v>
+        <v>172300</v>
       </c>
     </row>
     <row r="121">
@@ -2003,11 +2003,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Berberin 10mg Pharimexco (c/100v)</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>172300</v>
+        <v>11100</v>
       </c>
     </row>
     <row r="122">
@@ -2016,11 +2016,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Tomax genta bình nguyên (lốc/10t/6gr)</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11100</v>
+        <v>79300</v>
       </c>
     </row>
     <row r="123">
@@ -2029,11 +2029,11 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Berlthyrox 100mcg menarini (h/100v)</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>79300</v>
+        <v>86200</v>
       </c>
     </row>
     <row r="124">
@@ -2042,11 +2042,11 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Trifungi itraconazol 100mg pymepharco (h/4v)</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>86200</v>
+        <v>19900</v>
       </c>
     </row>
     <row r="125">
@@ -2055,11 +2055,11 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Nhỏ mắt osla merap (c/15ml)</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>19900</v>
+        <v>21400</v>
       </c>
     </row>
     <row r="126">
@@ -2068,11 +2068,11 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Yumangel yuhan (h/20g/15ml)</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>21400</v>
+        <v>96100</v>
       </c>
     </row>
     <row r="127">
@@ -2081,11 +2081,11 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Nhỏ mắt mũi natri clorid 0.9% pharmedic (lốc/10c/10ml)</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>96100</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="128">
@@ -2094,11 +2094,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Men hỗ trợ tiêu hóa Enterogermina gut defense 2 billion/5ml Opella (H/20o/5ml)</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>30500</v>
+        <v>178600</v>
       </c>
     </row>
     <row r="129">
@@ -2107,11 +2107,11 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Mepraz omeprazol 20mg sanofi (hộp/28 viên nang)</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>178600</v>
+        <v>114600</v>
       </c>
     </row>
     <row r="130">
@@ -2120,11 +2120,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Nhỏ Mắt Sanlein 0.1% Santen (C/5ml)</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>114600</v>
+        <v>64500</v>
       </c>
     </row>
     <row r="131">
@@ -2133,11 +2133,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Gel bôi trơn ky durex Reckitt Benckiser (T/50gr)</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>64500</v>
+        <v>71000</v>
       </c>
     </row>
     <row r="132">
@@ -2146,11 +2146,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Glucophage 500mg merck (h/50v)</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>71000</v>
+        <v>87100</v>
       </c>
     </row>
     <row r="133">
@@ -2159,11 +2159,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Siro Prospan Syrup Engelhard Arznelmittel (C/100ml)</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>87100</v>
+        <v>91900</v>
       </c>
     </row>
     <row r="134">
@@ -2172,11 +2172,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Dexamethason inj kabi (h/50o)</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>91900</v>
+        <v>98800</v>
       </c>
     </row>
     <row r="135">
@@ -2185,11 +2185,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Diamicron MR 60mg Servier (H/30v)</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>98800</v>
+        <v>207700</v>
       </c>
     </row>
     <row r="136">
@@ -2198,11 +2198,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Mimosa viên an thần opc (h/50v)</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>207700</v>
+        <v>75500</v>
       </c>
     </row>
     <row r="137">
@@ -2211,11 +2211,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Kremil-S United (h/100v)</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>75500</v>
+        <v>100400</v>
       </c>
     </row>
     <row r="138">
@@ -2224,11 +2224,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Silkron Cream Dongkwang (T/10gr) (bảy màu)</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>100400</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="139">
@@ -2237,11 +2237,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Glisan 30mg mr hasan (h/300v)</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>19800</v>
+        <v>242800</v>
       </c>
     </row>
     <row r="140">
@@ -2250,11 +2250,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Diamicron MR 30mg Servier (H/60v)</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>242800</v>
+        <v>213600</v>
       </c>
     </row>
     <row r="141">
@@ -2263,11 +2263,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Scanneuron stella (H/100v)</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>213600</v>
+        <v>111500</v>
       </c>
     </row>
     <row r="142">
@@ -2276,11 +2276,11 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Vitamin A D Phúc Vinh (h/100v)</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>111500</v>
+        <v>37000</v>
       </c>
     </row>
     <row r="143">
@@ -2289,11 +2289,11 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Dầu thái đỏ siang pure oil (lốc/12c/3ml) (nhỏ)</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>37000</v>
+        <v>190500</v>
       </c>
     </row>
     <row r="144">
@@ -2302,11 +2302,11 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Decolgen Forte United International (Hộp/30vỉ/4viên)</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>190500</v>
+        <v>137700</v>
       </c>
     </row>
     <row r="145">
@@ -2315,11 +2315,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Naphacogyl viên nam hà (h/20v)</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>137700</v>
+        <v>24300</v>
       </c>
     </row>
     <row r="146">
@@ -2328,11 +2328,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Prednisolone 5mg ngọt khapharco (c/1000v)</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>24300</v>
+        <v>157900</v>
       </c>
     </row>
     <row r="147">
@@ -2341,11 +2341,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Nhỏ Mắt Flumetholon 0.1% Santen (C/5ml)</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>157900</v>
+        <v>38800</v>
       </c>
     </row>
     <row r="148">
@@ -2354,11 +2354,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Amlodipin 5mg domesco (h/30v)</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>38800</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="149">
@@ -2367,11 +2367,11 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Acetylcystein 200mg khapharco (h/100v)</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>18600</v>
+        <v>31300</v>
       </c>
     </row>
     <row r="150">
@@ -2380,11 +2380,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Zoamco a amlodipin 5mg pmp (h/20v)</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>31300</v>
+        <v>41700</v>
       </c>
     </row>
     <row r="151">
@@ -2393,11 +2393,11 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Ho astex siro opc (c/90ml)</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>41700</v>
+        <v>35500</v>
       </c>
     </row>
     <row r="152">
@@ -2406,11 +2406,11 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Nhỏ Mắt Mydrin P Santen (C/10ml)</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>35500</v>
+        <v>66200</v>
       </c>
     </row>
     <row r="153">
@@ -2419,11 +2419,11 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Cravit Ophthalmic Solution 0.5% Santen (C/5ml)</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>66200</v>
+        <v>84300</v>
       </c>
     </row>
     <row r="154">
@@ -2432,11 +2432,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Hydrocolacyl prednisolon 5mg khapharco (h/200v)</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>84300</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="155">
@@ -2445,11 +2445,11 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Smecta Diosmectit 3g Ipsen (H/30g)</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>29500</v>
+        <v>154300</v>
       </c>
     </row>
     <row r="156">
@@ -2458,11 +2458,11 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Efferalgan Paracetamol 500mg UPSA SAS (H/40v)</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>154300</v>
+        <v>116300</v>
       </c>
     </row>
     <row r="157">
@@ -2471,11 +2471,11 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Dizzo effervescent tablets reliv (h/48v)</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>116300</v>
+        <v>146100</v>
       </c>
     </row>
     <row r="158">
@@ -2484,11 +2484,11 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Dầu phật linh trường sơn (h/12c/5ml)</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>146100</v>
+        <v>315400</v>
       </c>
     </row>
     <row r="159">
@@ -2497,11 +2497,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>V.Rohto Vitamin Rohto (C/13ml)</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>315400</v>
+        <v>54300</v>
       </c>
     </row>
     <row r="160">
@@ -2510,11 +2510,11 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Nhỏ Mắt Cravit Levofloxacin 1.5% Santen (C/5ml)</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>54300</v>
+        <v>123500</v>
       </c>
     </row>
     <row r="161">
@@ -2523,11 +2523,11 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Alpha choay sanofi (h/30v)</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>123500</v>
+        <v>68600</v>
       </c>
     </row>
     <row r="162">
@@ -2536,11 +2536,11 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Duphalac Abbott (H/20g/15ml)</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>68600</v>
+        <v>137700</v>
       </c>
     </row>
     <row r="163">
@@ -2549,11 +2549,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Cefcenat cefuroxim 500mg caplets tipharco (h/50v)</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>137700</v>
+        <v>130900</v>
       </c>
     </row>
     <row r="164">
@@ -2562,11 +2562,11 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Povidine 10% pharmedic (lốc/10c/20ml)</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>130900</v>
+        <v>75700</v>
       </c>
     </row>
     <row r="165">
@@ -2575,11 +2575,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Alaxan united (h/25v/4v) (xé)</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>75700</v>
+        <v>118900</v>
       </c>
     </row>
     <row r="166">
@@ -2588,11 +2588,11 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Combo 2 thùng nước muối sinh lý Vĩnh Phúc (thùng/12c/1000ml)</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>118900</v>
+        <v>268300</v>
       </c>
     </row>
     <row r="167">
@@ -2601,11 +2601,11 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Bơm tiêm 3cc 25gx1 vinahankook (h/100 cái)</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>268300</v>
+        <v>82200</v>
       </c>
     </row>
     <row r="168">
@@ -2614,11 +2614,11 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Xịt mũi xisat hồng trẻ em merap (lốc/5 chai/75ml)</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>82200</v>
+        <v>137000</v>
       </c>
     </row>
     <row r="169">
@@ -2627,11 +2627,11 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Augbactam 1g mekophar (h/14v)</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>137000</v>
+        <v>49100</v>
       </c>
     </row>
     <row r="170">
@@ -2640,11 +2640,11 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Combo 3 lốc Oxy già VP 3% Vĩnh Phúc (lốc/10c/60ml)</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>49100</v>
+        <v>61400</v>
       </c>
     </row>
     <row r="171">
@@ -2653,11 +2653,11 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Tanganil 500mg pierre fabre (h/30v)</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>61400</v>
+        <v>133100</v>
       </c>
     </row>
     <row r="172">
@@ -2666,11 +2666,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Tăm bông trẻ em cotton buds for kid Bông Bạch Tuyết (bịch/10gói/57que)</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>133100</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="173">
@@ -2679,11 +2679,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Miếng dán hạ sốt bye bye fever super cool đen hisamitsu (h/3g/2m)</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>30000</v>
+        <v>63300</v>
       </c>
     </row>
     <row r="174">
@@ -2692,11 +2692,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Dầu thái đỏ siang pure oil (lốc/6c/7ml) (lớn)</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>63300</v>
+        <v>178600</v>
       </c>
     </row>
     <row r="175">
@@ -2705,11 +2705,11 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Homtamin Ginseng Korea United Pharm (h/60v)</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>178600</v>
+        <v>139600</v>
       </c>
     </row>
     <row r="176">
@@ -2718,336 +2718,11 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
+          <t>Tăm bông người lớn cotton buds Bông Bạch Tuyết (bịch/10gói/42que)</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>139600</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
-        <v>176</v>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
         <v>30300</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>177</v>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>18300</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
-        <v>178</v>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>18300</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="n">
-        <v>179</v>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>50500</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="n">
-        <v>180</v>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>9300</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
-        <v>181</v>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>132200</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="n">
-        <v>182</v>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>21000</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
-        <v>183</v>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>82200</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n">
-        <v>184</v>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>14800</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>185</v>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>70200</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>186</v>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>233200</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>187</v>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>74700</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>188</v>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>75700</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>189</v>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>45100</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>190</v>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>29900</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>191</v>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>104100</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>192</v>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>155900</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>193</v>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>62400</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>194</v>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>20900</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>195</v>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>129300</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>196</v>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>216600</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>197</v>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>196400</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
-        <v>198</v>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>36900</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="n">
-        <v>199</v>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>178500</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
-        <v>200</v>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>TÊN THUỐC HAY DÙNG</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>173400</v>
       </c>
     </row>
   </sheetData>
